--- a/outputs/reanalysis5/zones/mites.xlsx
+++ b/outputs/reanalysis5/zones/mites.xlsx
@@ -691,7 +691,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mite_0000</t>
+          <t>mite_0058</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mite_0001</t>
+          <t>mite_0059</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mite_0002</t>
+          <t>mite_0060</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mite_0004</t>
+          <t>mite_0062</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mite_0005</t>
+          <t>mite_0063</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mite_0007</t>
+          <t>mite_0065</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mite_0008</t>
+          <t>mite_0066</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mite_0009</t>
+          <t>mite_0067</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mite_0010</t>
+          <t>mite_0068</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mite_0011</t>
+          <t>mite_0069</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mite_0013</t>
+          <t>mite_0071</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mite_0014</t>
+          <t>mite_0072</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mite_0016</t>
+          <t>mite_0074</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mite_0018</t>
+          <t>mite_0076</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mite_0020</t>
+          <t>mite_0078</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mite_0022</t>
+          <t>mite_0080</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mite_0028</t>
+          <t>mite_0086</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mite_0030</t>
+          <t>mite_0088</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mite_0031</t>
+          <t>mite_0089</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mite_0032</t>
+          <t>mite_0090</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mite_0035</t>
+          <t>mite_0093</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mite_0036</t>
+          <t>mite_0094</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mite_0037</t>
+          <t>mite_0095</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mite_0039</t>
+          <t>mite_0097</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mite_0040</t>
+          <t>mite_0098</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mite_0041</t>
+          <t>mite_0099</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mite_0042</t>
+          <t>mite_0100</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mite_0045</t>
+          <t>mite_0103</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mite_0047</t>
+          <t>mite_0105</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mite_0051</t>
+          <t>mite_0109</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mite_0054</t>
+          <t>mite_0112</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mite_0055</t>
+          <t>mite_0113</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mite_0056</t>
+          <t>mite_0114</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mite_0057</t>
+          <t>mite_0115</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mite_0003</t>
+          <t>mite_0061</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mite_0006</t>
+          <t>mite_0064</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2437,7 +2437,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mite_0012</t>
+          <t>mite_0070</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mite_0017</t>
+          <t>mite_0075</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2531,7 +2531,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mite_0019</t>
+          <t>mite_0077</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mite_0021</t>
+          <t>mite_0079</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2625,7 +2625,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mite_0023</t>
+          <t>mite_0081</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2672,7 +2672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mite_0024</t>
+          <t>mite_0082</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mite_0025</t>
+          <t>mite_0083</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2766,7 +2766,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mite_0026</t>
+          <t>mite_0084</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mite_0027</t>
+          <t>mite_0085</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mite_0029</t>
+          <t>mite_0087</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2907,7 +2907,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mite_0033</t>
+          <t>mite_0091</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2954,7 +2954,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mite_0034</t>
+          <t>mite_0092</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mite_0038</t>
+          <t>mite_0096</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3048,7 +3048,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mite_0043</t>
+          <t>mite_0101</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mite_0044</t>
+          <t>mite_0102</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mite_0046</t>
+          <t>mite_0104</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mite_0048</t>
+          <t>mite_0106</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mite_0049</t>
+          <t>mite_0107</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mite_0050</t>
+          <t>mite_0108</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3330,7 +3330,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mite_0052</t>
+          <t>mite_0110</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mite_0053</t>
+          <t>mite_0111</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
